--- a/contoh/Format_Label_Dus.xlsx
+++ b/contoh/Format_Label_Dus.xlsx
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:Q82"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -485,13 +485,14 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="21.83203125" customWidth="1"/>
     <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="11.83203125" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" customWidth="1"/>
     <col min="13" max="13" width="9.83203125" customWidth="1"/>
     <col min="14" max="14" width="9.83203125" customWidth="1"/>
     <col min="15" max="15" width="9.83203125" customWidth="1"/>
-    <col min="16" max="16" width="13.83203125" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" customWidth="1"/>
+    <col min="17" max="17" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -557,24 +558,27 @@
         <v>Tanggal Terima</v>
       </c>
       <c r="J4" t="str">
+        <v>Kadaluarsa</v>
+      </c>
+      <c r="K4" t="str">
         <v>No GRN/SJ</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>Supplier</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>Lokasi</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>Zona</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>Status</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>PIC</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>Keterangan</v>
       </c>
     </row>
@@ -606,25 +610,28 @@
       <c r="I5" s="1">
         <v>46126</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J5" s="1">
+        <v>46700</v>
+      </c>
+      <c r="K5" t="str">
         <v>GRN-2604-01</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>G1-B4-S02</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>READY</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -657,24 +664,27 @@
         <v>46127</v>
       </c>
       <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
         <v>GRN-2604-02</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>G2-C2-S05</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v/>
       </c>
     </row>
@@ -707,24 +717,27 @@
         <v>46127</v>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>GRN-2604-02</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>G2-D1-S06</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>NEW</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v/>
       </c>
     </row>
@@ -757,24 +770,27 @@
         <v>46128</v>
       </c>
       <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
         <v>GRN-2604-03</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
       <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>NEW</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>SITI</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v/>
       </c>
     </row>
@@ -807,24 +823,27 @@
         <v>46128</v>
       </c>
       <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
         <v>GRN-2604-03</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
       <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>SITI</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <v/>
       </c>
     </row>
@@ -857,24 +876,27 @@
         <v>46128</v>
       </c>
       <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
         <v>GRN-2604-03</v>
       </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
       <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v>NEW</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>SITI</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <v/>
       </c>
     </row>
@@ -906,25 +928,28 @@
       <c r="I11" s="1">
         <v>46129</v>
       </c>
-      <c r="J11" t="str">
+      <c r="J11" s="1">
+        <v>46721</v>
+      </c>
+      <c r="K11" t="str">
         <v>GRN-2604-04</v>
       </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>G4-F2-S11</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <v/>
       </c>
     </row>
@@ -956,25 +981,28 @@
       <c r="I12" s="1">
         <v>46129</v>
       </c>
-      <c r="J12" t="str">
+      <c r="J12" s="1">
+        <v>46721</v>
+      </c>
+      <c r="K12" t="str">
         <v>GRN-2604-04</v>
       </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>G4-F3-S12</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>NEW</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <v/>
       </c>
     </row>
@@ -1006,25 +1034,28 @@
       <c r="I13" s="1">
         <v>46129</v>
       </c>
-      <c r="J13" t="str">
+      <c r="J13" s="1">
+        <v>46721</v>
+      </c>
+      <c r="K13" t="str">
         <v>GRN-2604-04</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>G4-A1-S13</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <v>READY</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <v/>
       </c>
     </row>
@@ -1056,25 +1087,28 @@
       <c r="I14" s="1">
         <v>46129</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J14" s="1">
+        <v>46721</v>
+      </c>
+      <c r="K14" t="str">
         <v>GRN-2604-04</v>
       </c>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
         <v>G4-B4-S14</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <v>READY</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P14" t="str">
+      <c r="Q14" t="str">
         <v/>
       </c>
     </row>
@@ -1107,24 +1141,27 @@
         <v>46130</v>
       </c>
       <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
         <v>GRN-2604-05</v>
       </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
         <v>G1-F3-S14</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v>NEW</v>
       </c>
-      <c r="N15" t="str">
+      <c r="O15" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="P15" t="str">
+      <c r="Q15" t="str">
         <v/>
       </c>
     </row>
@@ -1157,24 +1194,27 @@
         <v>46131</v>
       </c>
       <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
         <v>GRN-2604-06</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
       <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v>READY</v>
       </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P16" t="str">
+      <c r="Q16" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -1207,24 +1247,27 @@
         <v>46131</v>
       </c>
       <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
         <v>GRN-2604-06</v>
       </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
       <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N17" t="str">
+      <c r="O17" t="str">
         <v>READY</v>
       </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P17" t="str">
+      <c r="Q17" t="str">
         <v/>
       </c>
     </row>
@@ -1256,25 +1299,28 @@
       <c r="I18" s="1">
         <v>46132</v>
       </c>
-      <c r="J18" t="str">
+      <c r="J18" s="1">
+        <v>46742</v>
+      </c>
+      <c r="K18" t="str">
         <v>GRN-2604-07</v>
       </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L18" t="str">
+      <c r="M18" t="str">
         <v>G3-B4-S20</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <v>READY</v>
       </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
         <v>SITI</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
         <v/>
       </c>
     </row>
@@ -1306,25 +1352,28 @@
       <c r="I19" s="1">
         <v>46132</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J19" s="1">
+        <v>46742</v>
+      </c>
+      <c r="K19" t="str">
         <v>GRN-2604-07</v>
       </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
         <v>G3-C2-S01</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N19" t="str">
+      <c r="O19" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
         <v>SITI</v>
       </c>
-      <c r="P19" t="str">
+      <c r="Q19" t="str">
         <v/>
       </c>
     </row>
@@ -1356,25 +1405,28 @@
       <c r="I20" s="1">
         <v>46132</v>
       </c>
-      <c r="J20" t="str">
+      <c r="J20" s="1">
+        <v>46742</v>
+      </c>
+      <c r="K20" t="str">
         <v>GRN-2604-07</v>
       </c>
-      <c r="K20" t="str">
+      <c r="L20" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
         <v>G3-D1-S02</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <v>NEW</v>
       </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
         <v>SITI</v>
       </c>
-      <c r="P20" t="str">
+      <c r="Q20" t="str">
         <v/>
       </c>
     </row>
@@ -1407,24 +1459,27 @@
         <v>46133</v>
       </c>
       <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
         <v>GRN-2604-08</v>
       </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
         <v>G4-C2-S03</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N21" t="str">
+      <c r="O21" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P21" t="str">
+      <c r="Q21" t="str">
         <v/>
       </c>
     </row>
@@ -1457,24 +1512,27 @@
         <v>46133</v>
       </c>
       <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
         <v>GRN-2604-08</v>
       </c>
-      <c r="K22" t="str">
+      <c r="L22" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
         <v>G4-D1-S04</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <v>NEW</v>
       </c>
-      <c r="O22" t="str">
+      <c r="P22" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P22" t="str">
+      <c r="Q22" t="str">
         <v/>
       </c>
     </row>
@@ -1507,24 +1565,27 @@
         <v>46133</v>
       </c>
       <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
         <v>GRN-2604-08</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>G4-F2-S05</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O23" t="str">
+      <c r="P23" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P23" t="str">
+      <c r="Q23" t="str">
         <v/>
       </c>
     </row>
@@ -1557,24 +1618,27 @@
         <v>46133</v>
       </c>
       <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
         <v>GRN-2604-08</v>
       </c>
-      <c r="K24" t="str">
+      <c r="L24" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
         <v>G4-F3-S06</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N24" t="str">
+      <c r="O24" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O24" t="str">
+      <c r="P24" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P24" t="str">
+      <c r="Q24" t="str">
         <v/>
       </c>
     </row>
@@ -1607,24 +1671,27 @@
         <v>46134</v>
       </c>
       <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
         <v>GRN-2604-09</v>
       </c>
-      <c r="K25" t="str">
+      <c r="L25" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
         <v>G1-D1-S06</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N25" t="str">
+      <c r="O25" t="str">
         <v>NEW</v>
       </c>
-      <c r="O25" t="str">
+      <c r="P25" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="P25" t="str">
+      <c r="Q25" t="str">
         <v/>
       </c>
     </row>
@@ -1656,25 +1723,28 @@
       <c r="I26" s="1">
         <v>46126</v>
       </c>
-      <c r="J26" t="str">
+      <c r="J26" s="1">
+        <v>46763</v>
+      </c>
+      <c r="K26" t="str">
         <v>GRN-2604-10</v>
       </c>
-      <c r="K26" t="str">
+      <c r="L26" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
       <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N26" t="str">
+      <c r="O26" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O26" t="str">
+      <c r="P26" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P26" t="str">
+      <c r="Q26" t="str">
         <v/>
       </c>
     </row>
@@ -1706,25 +1776,28 @@
       <c r="I27" s="1">
         <v>46126</v>
       </c>
-      <c r="J27" t="str">
+      <c r="J27" s="1">
+        <v>46763</v>
+      </c>
+      <c r="K27" t="str">
         <v>GRN-2604-10</v>
       </c>
-      <c r="K27" t="str">
+      <c r="L27" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
       <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O27" t="str">
+      <c r="P27" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P27" t="str">
+      <c r="Q27" t="str">
         <v/>
       </c>
     </row>
@@ -1757,24 +1830,27 @@
         <v>46127</v>
       </c>
       <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
         <v>GRN-2604-11</v>
       </c>
-      <c r="K28" t="str">
+      <c r="L28" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
         <v>G3-F3-S12</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O28" t="str">
+      <c r="P28" t="str">
         <v>SITI</v>
       </c>
-      <c r="P28" t="str">
+      <c r="Q28" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -1807,24 +1883,27 @@
         <v>46127</v>
       </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
         <v>GRN-2604-11</v>
       </c>
-      <c r="K29" t="str">
+      <c r="L29" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L29" t="str">
+      <c r="M29" t="str">
         <v>G3-A1-S13</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
         <v>NEW</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <v>READY</v>
       </c>
-      <c r="O29" t="str">
+      <c r="P29" t="str">
         <v>SITI</v>
       </c>
-      <c r="P29" t="str">
+      <c r="Q29" t="str">
         <v/>
       </c>
     </row>
@@ -1857,24 +1936,27 @@
         <v>46127</v>
       </c>
       <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
         <v>GRN-2604-11</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>G3-B4-S14</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>READY</v>
       </c>
-      <c r="O30" t="str">
+      <c r="P30" t="str">
         <v>SITI</v>
       </c>
-      <c r="P30" t="str">
+      <c r="Q30" t="str">
         <v/>
       </c>
     </row>
@@ -1907,24 +1989,27 @@
         <v>46128</v>
       </c>
       <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
         <v>GRN-2604-12</v>
       </c>
-      <c r="K31" t="str">
+      <c r="L31" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L31" t="str">
+      <c r="M31" t="str">
         <v>G4-A1-S15</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
         <v>NEW</v>
       </c>
-      <c r="N31" t="str">
+      <c r="O31" t="str">
         <v>READY</v>
       </c>
-      <c r="O31" t="str">
+      <c r="P31" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P31" t="str">
+      <c r="Q31" t="str">
         <v/>
       </c>
     </row>
@@ -1957,24 +2042,27 @@
         <v>46128</v>
       </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
         <v>GRN-2604-12</v>
       </c>
-      <c r="K32" t="str">
+      <c r="L32" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L32" t="str">
+      <c r="M32" t="str">
         <v>G4-B4-S16</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N32" t="str">
+      <c r="O32" t="str">
         <v>READY</v>
       </c>
-      <c r="O32" t="str">
+      <c r="P32" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P32" t="str">
+      <c r="Q32" t="str">
         <v/>
       </c>
     </row>
@@ -2007,24 +2095,27 @@
         <v>46128</v>
       </c>
       <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
         <v>GRN-2604-12</v>
       </c>
-      <c r="K33" t="str">
+      <c r="L33" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L33" t="str">
+      <c r="M33" t="str">
         <v>G4-C2-S17</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N33" t="str">
+      <c r="O33" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O33" t="str">
+      <c r="P33" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P33" t="str">
+      <c r="Q33" t="str">
         <v/>
       </c>
     </row>
@@ -2057,24 +2148,27 @@
         <v>46128</v>
       </c>
       <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
         <v>GRN-2604-12</v>
       </c>
-      <c r="K34" t="str">
+      <c r="L34" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L34" t="str">
+      <c r="M34" t="str">
         <v>G4-D1-S18</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N34" t="str">
+      <c r="O34" t="str">
         <v>NEW</v>
       </c>
-      <c r="O34" t="str">
+      <c r="P34" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P34" t="str">
+      <c r="Q34" t="str">
         <v/>
       </c>
     </row>
@@ -2106,25 +2200,28 @@
       <c r="I35" s="1">
         <v>46129</v>
       </c>
-      <c r="J35" t="str">
+      <c r="J35" s="1">
+        <v>46784</v>
+      </c>
+      <c r="K35" t="str">
         <v>GRN-2604-13</v>
       </c>
-      <c r="K35" t="str">
+      <c r="L35" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
       <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N35" t="str">
+      <c r="O35" t="str">
         <v>READY</v>
       </c>
-      <c r="O35" t="str">
+      <c r="P35" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="P35" t="str">
+      <c r="Q35" t="str">
         <v/>
       </c>
     </row>
@@ -2157,24 +2254,27 @@
         <v>46130</v>
       </c>
       <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
         <v>GRN-2604-14</v>
       </c>
-      <c r="K36" t="str">
+      <c r="L36" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L36" t="str">
+      <c r="M36" t="str">
         <v>G2-C2-S01</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N36" t="str">
+      <c r="O36" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O36" t="str">
+      <c r="P36" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P36" t="str">
+      <c r="Q36" t="str">
         <v/>
       </c>
     </row>
@@ -2207,24 +2307,27 @@
         <v>46130</v>
       </c>
       <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
         <v>GRN-2604-14</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <v>G2-D1-S02</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N37" t="str">
+      <c r="O37" t="str">
         <v>NEW</v>
       </c>
-      <c r="O37" t="str">
+      <c r="P37" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P37" t="str">
+      <c r="Q37" t="str">
         <v/>
       </c>
     </row>
@@ -2257,24 +2360,27 @@
         <v>46131</v>
       </c>
       <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
         <v>GRN-2604-15</v>
       </c>
-      <c r="K38" t="str">
+      <c r="L38" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L38" t="str">
+      <c r="M38" t="str">
         <v>G3-D1-S04</v>
       </c>
-      <c r="M38" t="str">
+      <c r="N38" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N38" t="str">
+      <c r="O38" t="str">
         <v>NEW</v>
       </c>
-      <c r="O38" t="str">
+      <c r="P38" t="str">
         <v>SITI</v>
       </c>
-      <c r="P38" t="str">
+      <c r="Q38" t="str">
         <v/>
       </c>
     </row>
@@ -2307,24 +2413,27 @@
         <v>46131</v>
       </c>
       <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
         <v>GRN-2604-15</v>
       </c>
-      <c r="K39" t="str">
+      <c r="L39" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L39" t="str">
+      <c r="M39" t="str">
         <v>G3-F2-S05</v>
       </c>
-      <c r="M39" t="str">
+      <c r="N39" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N39" t="str">
+      <c r="O39" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O39" t="str">
+      <c r="P39" t="str">
         <v>SITI</v>
       </c>
-      <c r="P39" t="str">
+      <c r="Q39" t="str">
         <v/>
       </c>
     </row>
@@ -2357,24 +2466,27 @@
         <v>46131</v>
       </c>
       <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
         <v>GRN-2604-15</v>
       </c>
-      <c r="K40" t="str">
+      <c r="L40" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L40" t="str">
+      <c r="M40" t="str">
         <v>G3-F3-S06</v>
       </c>
-      <c r="M40" t="str">
+      <c r="N40" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N40" t="str">
+      <c r="O40" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O40" t="str">
+      <c r="P40" t="str">
         <v>SITI</v>
       </c>
-      <c r="P40" t="str">
+      <c r="Q40" t="str">
         <v/>
       </c>
     </row>
@@ -2406,25 +2518,28 @@
       <c r="I41" s="1">
         <v>46132</v>
       </c>
-      <c r="J41" t="str">
+      <c r="J41" s="1">
+        <v>46805</v>
+      </c>
+      <c r="K41" t="str">
         <v>GRN-2604-16</v>
       </c>
-      <c r="K41" t="str">
+      <c r="L41" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L41" t="str">
+      <c r="M41" t="str">
         <v>G4-F2-S07</v>
       </c>
-      <c r="M41" t="str">
+      <c r="N41" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N41" t="str">
+      <c r="O41" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O41" t="str">
+      <c r="P41" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P41" t="str">
+      <c r="Q41" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -2456,25 +2571,28 @@
       <c r="I42" s="1">
         <v>46132</v>
       </c>
-      <c r="J42" t="str">
+      <c r="J42" s="1">
+        <v>46805</v>
+      </c>
+      <c r="K42" t="str">
         <v>GRN-2604-16</v>
       </c>
-      <c r="K42" t="str">
+      <c r="L42" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L42" t="str">
+      <c r="M42" t="str">
         <v>G4-F3-S08</v>
       </c>
-      <c r="M42" t="str">
+      <c r="N42" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N42" t="str">
+      <c r="O42" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O42" t="str">
+      <c r="P42" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P42" t="str">
+      <c r="Q42" t="str">
         <v/>
       </c>
     </row>
@@ -2506,25 +2624,28 @@
       <c r="I43" s="1">
         <v>46132</v>
       </c>
-      <c r="J43" t="str">
+      <c r="J43" s="1">
+        <v>46805</v>
+      </c>
+      <c r="K43" t="str">
         <v>GRN-2604-16</v>
       </c>
-      <c r="K43" t="str">
+      <c r="L43" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L43" t="str">
+      <c r="M43" t="str">
         <v>G4-A1-S09</v>
       </c>
-      <c r="M43" t="str">
+      <c r="N43" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N43" t="str">
+      <c r="O43" t="str">
         <v>READY</v>
       </c>
-      <c r="O43" t="str">
+      <c r="P43" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P43" t="str">
+      <c r="Q43" t="str">
         <v/>
       </c>
     </row>
@@ -2556,25 +2677,28 @@
       <c r="I44" s="1">
         <v>46132</v>
       </c>
-      <c r="J44" t="str">
+      <c r="J44" s="1">
+        <v>46805</v>
+      </c>
+      <c r="K44" t="str">
         <v>GRN-2604-16</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <v>G4-B4-S10</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v>NEW</v>
       </c>
-      <c r="N44" t="str">
+      <c r="O44" t="str">
         <v>READY</v>
       </c>
-      <c r="O44" t="str">
+      <c r="P44" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P44" t="str">
+      <c r="Q44" t="str">
         <v/>
       </c>
     </row>
@@ -2607,24 +2731,27 @@
         <v>46133</v>
       </c>
       <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
         <v>GRN-2604-17</v>
       </c>
-      <c r="K45" t="str">
+      <c r="L45" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
       <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N45" t="str">
+      <c r="O45" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O45" t="str">
+      <c r="P45" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="P45" t="str">
+      <c r="Q45" t="str">
         <v/>
       </c>
     </row>
@@ -2657,24 +2784,27 @@
         <v>46134</v>
       </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
         <v>GRN-2604-18</v>
       </c>
-      <c r="K46" t="str">
+      <c r="L46" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L46" t="str">
+      <c r="M46" t="str">
         <v>G2-A1-S13</v>
       </c>
-      <c r="M46" t="str">
+      <c r="N46" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N46" t="str">
+      <c r="O46" t="str">
         <v>READY</v>
       </c>
-      <c r="O46" t="str">
+      <c r="P46" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P46" t="str">
+      <c r="Q46" t="str">
         <v/>
       </c>
     </row>
@@ -2707,24 +2837,27 @@
         <v>46134</v>
       </c>
       <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
         <v>GRN-2604-18</v>
       </c>
-      <c r="K47" t="str">
+      <c r="L47" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L47" t="str">
+      <c r="M47" t="str">
         <v>G2-B4-S14</v>
       </c>
-      <c r="M47" t="str">
+      <c r="N47" t="str">
         <v>NEW</v>
       </c>
-      <c r="N47" t="str">
+      <c r="O47" t="str">
         <v>READY</v>
       </c>
-      <c r="O47" t="str">
+      <c r="P47" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P47" t="str">
+      <c r="Q47" t="str">
         <v/>
       </c>
     </row>
@@ -2756,25 +2889,28 @@
       <c r="I48" s="1">
         <v>46126</v>
       </c>
-      <c r="J48" t="str">
+      <c r="J48" s="1">
+        <v>46826</v>
+      </c>
+      <c r="K48" t="str">
         <v>GRN-2604-19</v>
       </c>
-      <c r="K48" t="str">
+      <c r="L48" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L48" t="str">
+      <c r="M48" t="str">
         <v>G3-B4-S16</v>
       </c>
-      <c r="M48" t="str">
+      <c r="N48" t="str">
         <v>NEW</v>
       </c>
-      <c r="N48" t="str">
+      <c r="O48" t="str">
         <v>READY</v>
       </c>
-      <c r="O48" t="str">
+      <c r="P48" t="str">
         <v>SITI</v>
       </c>
-      <c r="P48" t="str">
+      <c r="Q48" t="str">
         <v/>
       </c>
     </row>
@@ -2806,25 +2942,28 @@
       <c r="I49" s="1">
         <v>46126</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J49" s="1">
+        <v>46826</v>
+      </c>
+      <c r="K49" t="str">
         <v>GRN-2604-19</v>
       </c>
-      <c r="K49" t="str">
+      <c r="L49" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L49" t="str">
+      <c r="M49" t="str">
         <v>G3-C2-S17</v>
       </c>
-      <c r="M49" t="str">
+      <c r="N49" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N49" t="str">
+      <c r="O49" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O49" t="str">
+      <c r="P49" t="str">
         <v>SITI</v>
       </c>
-      <c r="P49" t="str">
+      <c r="Q49" t="str">
         <v/>
       </c>
     </row>
@@ -2856,25 +2995,28 @@
       <c r="I50" s="1">
         <v>46126</v>
       </c>
-      <c r="J50" t="str">
+      <c r="J50" s="1">
+        <v>46826</v>
+      </c>
+      <c r="K50" t="str">
         <v>GRN-2604-19</v>
       </c>
-      <c r="K50" t="str">
+      <c r="L50" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L50" t="str">
+      <c r="M50" t="str">
         <v>G3-D1-S18</v>
       </c>
-      <c r="M50" t="str">
+      <c r="N50" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N50" t="str">
+      <c r="O50" t="str">
         <v>NEW</v>
       </c>
-      <c r="O50" t="str">
+      <c r="P50" t="str">
         <v>SITI</v>
       </c>
-      <c r="P50" t="str">
+      <c r="Q50" t="str">
         <v/>
       </c>
     </row>
@@ -2907,24 +3049,27 @@
         <v>46127</v>
       </c>
       <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
         <v>GRN-2604-20</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
       <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N51" t="str">
+      <c r="O51" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O51" t="str">
+      <c r="P51" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P51" t="str">
+      <c r="Q51" t="str">
         <v/>
       </c>
     </row>
@@ -2957,24 +3102,27 @@
         <v>46127</v>
       </c>
       <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
         <v>GRN-2604-20</v>
       </c>
-      <c r="K52" t="str">
+      <c r="L52" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L52" t="str">
-        <v/>
-      </c>
       <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N52" t="str">
+      <c r="O52" t="str">
         <v>NEW</v>
       </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P52" t="str">
+      <c r="Q52" t="str">
         <v/>
       </c>
     </row>
@@ -3007,24 +3155,27 @@
         <v>46127</v>
       </c>
       <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
         <v>GRN-2604-20</v>
       </c>
-      <c r="K53" t="str">
+      <c r="L53" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L53" t="str">
-        <v/>
-      </c>
       <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N53" t="str">
+      <c r="O53" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O53" t="str">
+      <c r="P53" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P53" t="str">
+      <c r="Q53" t="str">
         <v/>
       </c>
     </row>
@@ -3057,24 +3208,27 @@
         <v>46127</v>
       </c>
       <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
         <v>GRN-2604-20</v>
       </c>
-      <c r="K54" t="str">
+      <c r="L54" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
       <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N54" t="str">
+      <c r="O54" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O54" t="str">
+      <c r="P54" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P54" t="str">
+      <c r="Q54" t="str">
         <v/>
       </c>
     </row>
@@ -3107,24 +3261,27 @@
         <v>46128</v>
       </c>
       <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
         <v>GRN-2604-21</v>
       </c>
-      <c r="K55" t="str">
+      <c r="L55" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="L55" t="str">
+      <c r="M55" t="str">
         <v>G1-D1-S02</v>
       </c>
-      <c r="M55" t="str">
+      <c r="N55" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N55" t="str">
+      <c r="O55" t="str">
         <v>NEW</v>
       </c>
-      <c r="O55" t="str">
+      <c r="P55" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="P55" t="str">
+      <c r="Q55" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -3156,25 +3313,28 @@
       <c r="I56" s="1">
         <v>46129</v>
       </c>
-      <c r="J56" t="str">
+      <c r="J56" s="1">
+        <v>46847</v>
+      </c>
+      <c r="K56" t="str">
         <v>GRN-2604-22</v>
       </c>
-      <c r="K56" t="str">
+      <c r="L56" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L56" t="str">
+      <c r="M56" t="str">
         <v>G2-F2-S05</v>
       </c>
-      <c r="M56" t="str">
+      <c r="N56" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N56" t="str">
+      <c r="O56" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O56" t="str">
+      <c r="P56" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P56" t="str">
+      <c r="Q56" t="str">
         <v/>
       </c>
     </row>
@@ -3206,25 +3366,28 @@
       <c r="I57" s="1">
         <v>46129</v>
       </c>
-      <c r="J57" t="str">
+      <c r="J57" s="1">
+        <v>46847</v>
+      </c>
+      <c r="K57" t="str">
         <v>GRN-2604-22</v>
       </c>
-      <c r="K57" t="str">
+      <c r="L57" t="str">
         <v>SINAR JAYA</v>
       </c>
-      <c r="L57" t="str">
+      <c r="M57" t="str">
         <v>G2-F3-S06</v>
       </c>
-      <c r="M57" t="str">
+      <c r="N57" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N57" t="str">
+      <c r="O57" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O57" t="str">
+      <c r="P57" t="str">
         <v>RUDI</v>
       </c>
-      <c r="P57" t="str">
+      <c r="Q57" t="str">
         <v/>
       </c>
     </row>
@@ -3257,24 +3420,27 @@
         <v>46130</v>
       </c>
       <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
         <v>GRN-2604-23</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <v>G3-F3-S08</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O58" t="str">
+      <c r="P58" t="str">
         <v>SITI</v>
       </c>
-      <c r="P58" t="str">
+      <c r="Q58" t="str">
         <v/>
       </c>
     </row>
@@ -3307,24 +3473,27 @@
         <v>46130</v>
       </c>
       <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
         <v>GRN-2604-23</v>
       </c>
-      <c r="K59" t="str">
+      <c r="L59" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L59" t="str">
+      <c r="M59" t="str">
         <v>G3-A1-S09</v>
       </c>
-      <c r="M59" t="str">
+      <c r="N59" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N59" t="str">
+      <c r="O59" t="str">
         <v>READY</v>
       </c>
-      <c r="O59" t="str">
+      <c r="P59" t="str">
         <v>SITI</v>
       </c>
-      <c r="P59" t="str">
+      <c r="Q59" t="str">
         <v/>
       </c>
     </row>
@@ -3357,24 +3526,27 @@
         <v>46130</v>
       </c>
       <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
         <v>GRN-2604-23</v>
       </c>
-      <c r="K60" t="str">
+      <c r="L60" t="str">
         <v>ANUGRAH MANDIRI</v>
       </c>
-      <c r="L60" t="str">
+      <c r="M60" t="str">
         <v>G3-B4-S10</v>
       </c>
-      <c r="M60" t="str">
+      <c r="N60" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N60" t="str">
+      <c r="O60" t="str">
         <v>READY</v>
       </c>
-      <c r="O60" t="str">
+      <c r="P60" t="str">
         <v>SITI</v>
       </c>
-      <c r="P60" t="str">
+      <c r="Q60" t="str">
         <v/>
       </c>
     </row>
@@ -3407,24 +3579,27 @@
         <v>46131</v>
       </c>
       <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
         <v>GRN-2604-24</v>
       </c>
-      <c r="K61" t="str">
+      <c r="L61" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
       <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N61" t="str">
+      <c r="O61" t="str">
         <v>READY</v>
       </c>
-      <c r="O61" t="str">
+      <c r="P61" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P61" t="str">
+      <c r="Q61" t="str">
         <v/>
       </c>
     </row>
@@ -3457,24 +3632,27 @@
         <v>46131</v>
       </c>
       <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
         <v>GRN-2604-24</v>
       </c>
-      <c r="K62" t="str">
+      <c r="L62" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L62" t="str">
-        <v/>
-      </c>
       <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N62" t="str">
+      <c r="O62" t="str">
         <v>READY</v>
       </c>
-      <c r="O62" t="str">
+      <c r="P62" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P62" t="str">
+      <c r="Q62" t="str">
         <v/>
       </c>
     </row>
@@ -3507,24 +3685,27 @@
         <v>46131</v>
       </c>
       <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
         <v>GRN-2604-24</v>
       </c>
-      <c r="K63" t="str">
+      <c r="L63" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L63" t="str">
-        <v/>
-      </c>
       <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v>NEW</v>
       </c>
-      <c r="N63" t="str">
+      <c r="O63" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O63" t="str">
+      <c r="P63" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P63" t="str">
+      <c r="Q63" t="str">
         <v/>
       </c>
     </row>
@@ -3557,228 +3738,231 @@
         <v>46131</v>
       </c>
       <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
         <v>GRN-2604-24</v>
       </c>
-      <c r="K64" t="str">
+      <c r="L64" t="str">
         <v>CAHAYA LOGISTIK</v>
       </c>
-      <c r="L64" t="str">
-        <v/>
-      </c>
       <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N64" t="str">
+      <c r="O64" t="str">
         <v>NEW</v>
       </c>
-      <c r="O64" t="str">
+      <c r="P64" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="P64" t="str">
+      <c r="Q64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="M65" t="str">
+      <c r="N65" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N65" t="str">
+      <c r="O65" t="str">
         <v>READY</v>
       </c>
-      <c r="O65" t="str">
+      <c r="P65" t="str">
         <v>MEEPLUS</v>
       </c>
     </row>
     <row r="66">
-      <c r="M66" t="str">
+      <c r="N66" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N66" t="str">
+      <c r="O66" t="str">
         <v>READY</v>
       </c>
-      <c r="O66" t="str">
+      <c r="P66" t="str">
         <v>RUDI</v>
       </c>
     </row>
     <row r="67">
-      <c r="M67" t="str">
+      <c r="N67" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N67" t="str">
+      <c r="O67" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O67" t="str">
+      <c r="P67" t="str">
         <v>SITI</v>
       </c>
     </row>
     <row r="68">
-      <c r="M68" t="str">
+      <c r="N68" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N68" t="str">
+      <c r="O68" t="str">
         <v>NEW</v>
       </c>
-      <c r="O68" t="str">
+      <c r="P68" t="str">
         <v>BAGAS</v>
       </c>
     </row>
     <row r="69">
-      <c r="M69" t="str">
+      <c r="N69" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N69" t="str">
+      <c r="O69" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O69" t="str">
+      <c r="P69" t="str">
         <v>MEEPLUS</v>
       </c>
     </row>
     <row r="70">
-      <c r="M70" t="str">
+      <c r="N70" t="str">
         <v>NEW</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O70" t="str">
+      <c r="P70" t="str">
         <v>RUDI</v>
       </c>
     </row>
     <row r="71">
-      <c r="M71" t="str">
+      <c r="N71" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N71" t="str">
+      <c r="O71" t="str">
         <v>READY</v>
       </c>
-      <c r="O71" t="str">
+      <c r="P71" t="str">
         <v>SITI</v>
       </c>
     </row>
     <row r="72">
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <v>READY</v>
       </c>
-      <c r="O72" t="str">
+      <c r="P72" t="str">
         <v>BAGAS</v>
       </c>
     </row>
     <row r="73">
-      <c r="M73" t="str">
+      <c r="N73" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N73" t="str">
+      <c r="O73" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O73" t="str">
+      <c r="P73" t="str">
         <v>MEEPLUS</v>
       </c>
     </row>
     <row r="74">
-      <c r="M74" t="str">
+      <c r="N74" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N74" t="str">
+      <c r="O74" t="str">
         <v>NEW</v>
       </c>
-      <c r="O74" t="str">
+      <c r="P74" t="str">
         <v>RUDI</v>
       </c>
     </row>
     <row r="75">
-      <c r="M75" t="str">
+      <c r="N75" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N75" t="str">
+      <c r="O75" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O75" t="str">
+      <c r="P75" t="str">
         <v>SITI</v>
       </c>
     </row>
     <row r="76">
-      <c r="M76" t="str">
+      <c r="N76" t="str">
         <v>MERAH</v>
       </c>
-      <c r="N76" t="str">
+      <c r="O76" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O76" t="str">
+      <c r="P76" t="str">
         <v>BAGAS</v>
       </c>
     </row>
     <row r="77">
-      <c r="M77" t="str">
+      <c r="N77" t="str">
         <v>NEW</v>
       </c>
-      <c r="N77" t="str">
+      <c r="O77" t="str">
         <v>READY</v>
       </c>
-      <c r="O77" t="str">
+      <c r="P77" t="str">
         <v>MEEPLUS</v>
       </c>
     </row>
     <row r="78">
-      <c r="M78" t="str">
+      <c r="N78" t="str">
         <v>HOLD</v>
       </c>
-      <c r="N78" t="str">
+      <c r="O78" t="str">
         <v>READY</v>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <v>RUDI</v>
       </c>
     </row>
     <row r="79">
-      <c r="M79" t="str">
+      <c r="N79" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N79" t="str">
+      <c r="O79" t="str">
         <v>PENDING</v>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <v>SITI</v>
       </c>
     </row>
     <row r="80">
-      <c r="M80" t="str">
+      <c r="N80" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N80" t="str">
+      <c r="O80" t="str">
         <v>NEW</v>
       </c>
-      <c r="O80" t="str">
+      <c r="P80" t="str">
         <v>BAGAS</v>
       </c>
     </row>
     <row r="81">
-      <c r="M81" t="str">
+      <c r="N81" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="N81" t="str">
+      <c r="O81" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O81" t="str">
+      <c r="P81" t="str">
         <v>MEEPLUS</v>
       </c>
     </row>
     <row r="82">
-      <c r="M82" t="str">
+      <c r="N82" t="str">
         <v>KUNING</v>
       </c>
-      <c r="N82" t="str">
+      <c r="O82" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="O82" t="str">
+      <c r="P82" t="str">
         <v>RUDI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q82"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/contoh/Format_Label_Dus.xlsx
+++ b/contoh/Format_Label_Dus.xlsx
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:P82"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -485,14 +485,13 @@
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="21.83203125" customWidth="1"/>
     <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" customWidth="1"/>
     <col min="13" max="13" width="9.83203125" customWidth="1"/>
     <col min="14" max="14" width="9.83203125" customWidth="1"/>
     <col min="15" max="15" width="9.83203125" customWidth="1"/>
-    <col min="16" max="16" width="9.83203125" customWidth="1"/>
-    <col min="17" max="17" width="13.83203125" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,27 +557,24 @@
         <v>Tanggal Terima</v>
       </c>
       <c r="J4" t="str">
-        <v>Kadaluarsa</v>
+        <v>No GRN/SJ</v>
       </c>
       <c r="K4" t="str">
-        <v>No GRN/SJ</v>
+        <v>Supplier</v>
       </c>
       <c r="L4" t="str">
-        <v>Supplier</v>
+        <v>Lokasi</v>
       </c>
       <c r="M4" t="str">
-        <v>Lokasi</v>
+        <v>Zona</v>
       </c>
       <c r="N4" t="str">
-        <v>Zona</v>
+        <v>Status</v>
       </c>
       <c r="O4" t="str">
-        <v>Status</v>
+        <v>PIC</v>
       </c>
       <c r="P4" t="str">
-        <v>PIC</v>
-      </c>
-      <c r="Q4" t="str">
         <v>Keterangan</v>
       </c>
     </row>
@@ -610,28 +606,25 @@
       <c r="I5" s="1">
         <v>46126</v>
       </c>
-      <c r="J5" s="1">
-        <v>46700</v>
+      <c r="J5" t="str">
+        <v>GRN-2604-01</v>
       </c>
       <c r="K5" t="str">
-        <v>GRN-2604-01</v>
+        <v>MEEPLUS</v>
       </c>
       <c r="L5" t="str">
+        <v>G1-B4-S02</v>
+      </c>
+      <c r="M5" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N5" t="str">
+        <v>READY</v>
+      </c>
+      <c r="O5" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="M5" t="str">
-        <v>G1-B4-S02</v>
-      </c>
-      <c r="N5" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O5" t="str">
-        <v>READY</v>
-      </c>
       <c r="P5" t="str">
-        <v>MEEPLUS</v>
-      </c>
-      <c r="Q5" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -664,27 +657,24 @@
         <v>46127</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>GRN-2604-02</v>
       </c>
       <c r="K6" t="str">
-        <v>GRN-2604-02</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L6" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-C2-S05</v>
       </c>
       <c r="M6" t="str">
-        <v>G2-C2-S05</v>
+        <v>HIJAU</v>
       </c>
       <c r="N6" t="str">
-        <v>HIJAU</v>
+        <v>PENDING</v>
       </c>
       <c r="O6" t="str">
-        <v>PENDING</v>
+        <v>RUDI</v>
       </c>
       <c r="P6" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q6" t="str">
         <v/>
       </c>
     </row>
@@ -717,27 +707,24 @@
         <v>46127</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>GRN-2604-02</v>
       </c>
       <c r="K7" t="str">
-        <v>GRN-2604-02</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L7" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-D1-S06</v>
       </c>
       <c r="M7" t="str">
-        <v>G2-D1-S06</v>
+        <v>KUNING</v>
       </c>
       <c r="N7" t="str">
-        <v>KUNING</v>
+        <v>NEW</v>
       </c>
       <c r="O7" t="str">
-        <v>NEW</v>
+        <v>RUDI</v>
       </c>
       <c r="P7" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q7" t="str">
         <v/>
       </c>
     </row>
@@ -770,27 +757,24 @@
         <v>46128</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>GRN-2604-03</v>
       </c>
       <c r="K8" t="str">
-        <v>GRN-2604-03</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L8" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>KUNING</v>
       </c>
       <c r="N8" t="str">
-        <v>KUNING</v>
+        <v>NEW</v>
       </c>
       <c r="O8" t="str">
-        <v>NEW</v>
+        <v>SITI</v>
       </c>
       <c r="P8" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q8" t="str">
         <v/>
       </c>
     </row>
@@ -823,27 +807,24 @@
         <v>46128</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>GRN-2604-03</v>
       </c>
       <c r="K9" t="str">
-        <v>GRN-2604-03</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L9" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v/>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>MERAH</v>
       </c>
       <c r="N9" t="str">
-        <v>MERAH</v>
+        <v>HOLD</v>
       </c>
       <c r="O9" t="str">
-        <v>HOLD</v>
+        <v>SITI</v>
       </c>
       <c r="P9" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q9" t="str">
         <v/>
       </c>
     </row>
@@ -876,27 +857,24 @@
         <v>46128</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>GRN-2604-03</v>
       </c>
       <c r="K10" t="str">
-        <v>GRN-2604-03</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L10" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v/>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="N10" t="str">
-        <v>NEW</v>
+        <v>RUSAK</v>
       </c>
       <c r="O10" t="str">
-        <v>RUSAK</v>
+        <v>SITI</v>
       </c>
       <c r="P10" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q10" t="str">
         <v/>
       </c>
     </row>
@@ -928,28 +906,25 @@
       <c r="I11" s="1">
         <v>46129</v>
       </c>
-      <c r="J11" s="1">
-        <v>46721</v>
+      <c r="J11" t="str">
+        <v>GRN-2604-04</v>
       </c>
       <c r="K11" t="str">
-        <v>GRN-2604-04</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L11" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-F2-S11</v>
       </c>
       <c r="M11" t="str">
-        <v>G4-F2-S11</v>
+        <v>MERAH</v>
       </c>
       <c r="N11" t="str">
-        <v>MERAH</v>
+        <v>HOLD</v>
       </c>
       <c r="O11" t="str">
-        <v>HOLD</v>
+        <v>BAGAS</v>
       </c>
       <c r="P11" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q11" t="str">
         <v/>
       </c>
     </row>
@@ -981,28 +956,25 @@
       <c r="I12" s="1">
         <v>46129</v>
       </c>
-      <c r="J12" s="1">
-        <v>46721</v>
+      <c r="J12" t="str">
+        <v>GRN-2604-04</v>
       </c>
       <c r="K12" t="str">
-        <v>GRN-2604-04</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L12" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-F3-S12</v>
       </c>
       <c r="M12" t="str">
-        <v>G4-F3-S12</v>
+        <v>NEW</v>
       </c>
       <c r="N12" t="str">
-        <v>NEW</v>
+        <v>RUSAK</v>
       </c>
       <c r="O12" t="str">
-        <v>RUSAK</v>
+        <v>BAGAS</v>
       </c>
       <c r="P12" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q12" t="str">
         <v/>
       </c>
     </row>
@@ -1034,28 +1006,25 @@
       <c r="I13" s="1">
         <v>46129</v>
       </c>
-      <c r="J13" s="1">
-        <v>46721</v>
+      <c r="J13" t="str">
+        <v>GRN-2604-04</v>
       </c>
       <c r="K13" t="str">
-        <v>GRN-2604-04</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L13" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-A1-S13</v>
       </c>
       <c r="M13" t="str">
-        <v>G4-A1-S13</v>
+        <v>HOLD</v>
       </c>
       <c r="N13" t="str">
-        <v>HOLD</v>
+        <v>READY</v>
       </c>
       <c r="O13" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P13" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q13" t="str">
         <v/>
       </c>
     </row>
@@ -1087,28 +1056,25 @@
       <c r="I14" s="1">
         <v>46129</v>
       </c>
-      <c r="J14" s="1">
-        <v>46721</v>
+      <c r="J14" t="str">
+        <v>GRN-2604-04</v>
       </c>
       <c r="K14" t="str">
-        <v>GRN-2604-04</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L14" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-B4-S14</v>
       </c>
       <c r="M14" t="str">
-        <v>G4-B4-S14</v>
+        <v>HIJAU</v>
       </c>
       <c r="N14" t="str">
-        <v>HIJAU</v>
+        <v>READY</v>
       </c>
       <c r="O14" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P14" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q14" t="str">
         <v/>
       </c>
     </row>
@@ -1141,27 +1107,24 @@
         <v>46130</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>GRN-2604-05</v>
       </c>
       <c r="K15" t="str">
-        <v>GRN-2604-05</v>
+        <v>MEEPLUS</v>
       </c>
       <c r="L15" t="str">
+        <v>G1-F3-S14</v>
+      </c>
+      <c r="M15" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="N15" t="str">
+        <v>RUSAK</v>
+      </c>
+      <c r="O15" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="M15" t="str">
-        <v>G1-F3-S14</v>
-      </c>
-      <c r="N15" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="O15" t="str">
-        <v>RUSAK</v>
-      </c>
       <c r="P15" t="str">
-        <v>MEEPLUS</v>
-      </c>
-      <c r="Q15" t="str">
         <v/>
       </c>
     </row>
@@ -1194,27 +1157,24 @@
         <v>46131</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>GRN-2604-06</v>
       </c>
       <c r="K16" t="str">
-        <v>GRN-2604-06</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L16" t="str">
-        <v>SINAR JAYA</v>
+        <v/>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>HOLD</v>
       </c>
       <c r="N16" t="str">
-        <v>HOLD</v>
+        <v>READY</v>
       </c>
       <c r="O16" t="str">
-        <v>READY</v>
+        <v>RUDI</v>
       </c>
       <c r="P16" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q16" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -1247,27 +1207,24 @@
         <v>46131</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>GRN-2604-06</v>
       </c>
       <c r="K17" t="str">
-        <v>GRN-2604-06</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L17" t="str">
-        <v>SINAR JAYA</v>
+        <v/>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>HIJAU</v>
       </c>
       <c r="N17" t="str">
-        <v>HIJAU</v>
+        <v>READY</v>
       </c>
       <c r="O17" t="str">
-        <v>READY</v>
+        <v>RUDI</v>
       </c>
       <c r="P17" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q17" t="str">
         <v/>
       </c>
     </row>
@@ -1299,28 +1256,25 @@
       <c r="I18" s="1">
         <v>46132</v>
       </c>
-      <c r="J18" s="1">
-        <v>46742</v>
+      <c r="J18" t="str">
+        <v>GRN-2604-07</v>
       </c>
       <c r="K18" t="str">
-        <v>GRN-2604-07</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L18" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-B4-S20</v>
       </c>
       <c r="M18" t="str">
-        <v>G3-B4-S20</v>
+        <v>HIJAU</v>
       </c>
       <c r="N18" t="str">
-        <v>HIJAU</v>
+        <v>READY</v>
       </c>
       <c r="O18" t="str">
-        <v>READY</v>
+        <v>SITI</v>
       </c>
       <c r="P18" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q18" t="str">
         <v/>
       </c>
     </row>
@@ -1352,28 +1306,25 @@
       <c r="I19" s="1">
         <v>46132</v>
       </c>
-      <c r="J19" s="1">
-        <v>46742</v>
+      <c r="J19" t="str">
+        <v>GRN-2604-07</v>
       </c>
       <c r="K19" t="str">
-        <v>GRN-2604-07</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L19" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-C2-S01</v>
       </c>
       <c r="M19" t="str">
-        <v>G3-C2-S01</v>
+        <v>HIJAU</v>
       </c>
       <c r="N19" t="str">
-        <v>HIJAU</v>
+        <v>PENDING</v>
       </c>
       <c r="O19" t="str">
-        <v>PENDING</v>
+        <v>SITI</v>
       </c>
       <c r="P19" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q19" t="str">
         <v/>
       </c>
     </row>
@@ -1405,28 +1356,25 @@
       <c r="I20" s="1">
         <v>46132</v>
       </c>
-      <c r="J20" s="1">
-        <v>46742</v>
+      <c r="J20" t="str">
+        <v>GRN-2604-07</v>
       </c>
       <c r="K20" t="str">
-        <v>GRN-2604-07</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L20" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-D1-S02</v>
       </c>
       <c r="M20" t="str">
-        <v>G3-D1-S02</v>
+        <v>HIJAU</v>
       </c>
       <c r="N20" t="str">
-        <v>HIJAU</v>
+        <v>NEW</v>
       </c>
       <c r="O20" t="str">
-        <v>NEW</v>
+        <v>SITI</v>
       </c>
       <c r="P20" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q20" t="str">
         <v/>
       </c>
     </row>
@@ -1459,27 +1407,24 @@
         <v>46133</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>GRN-2604-08</v>
       </c>
       <c r="K21" t="str">
-        <v>GRN-2604-08</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L21" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-C2-S03</v>
       </c>
       <c r="M21" t="str">
-        <v>G4-C2-S03</v>
+        <v>HIJAU</v>
       </c>
       <c r="N21" t="str">
-        <v>HIJAU</v>
+        <v>PENDING</v>
       </c>
       <c r="O21" t="str">
-        <v>PENDING</v>
+        <v>BAGAS</v>
       </c>
       <c r="P21" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q21" t="str">
         <v/>
       </c>
     </row>
@@ -1512,27 +1457,24 @@
         <v>46133</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>GRN-2604-08</v>
       </c>
       <c r="K22" t="str">
-        <v>GRN-2604-08</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L22" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-D1-S04</v>
       </c>
       <c r="M22" t="str">
-        <v>G4-D1-S04</v>
+        <v>HIJAU</v>
       </c>
       <c r="N22" t="str">
-        <v>HIJAU</v>
+        <v>NEW</v>
       </c>
       <c r="O22" t="str">
-        <v>NEW</v>
+        <v>BAGAS</v>
       </c>
       <c r="P22" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q22" t="str">
         <v/>
       </c>
     </row>
@@ -1565,27 +1507,24 @@
         <v>46133</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>GRN-2604-08</v>
       </c>
       <c r="K23" t="str">
-        <v>GRN-2604-08</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L23" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-F2-S05</v>
       </c>
       <c r="M23" t="str">
-        <v>G4-F2-S05</v>
+        <v>KUNING</v>
       </c>
       <c r="N23" t="str">
-        <v>KUNING</v>
+        <v>HOLD</v>
       </c>
       <c r="O23" t="str">
-        <v>HOLD</v>
+        <v>BAGAS</v>
       </c>
       <c r="P23" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q23" t="str">
         <v/>
       </c>
     </row>
@@ -1618,27 +1557,24 @@
         <v>46133</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>GRN-2604-08</v>
       </c>
       <c r="K24" t="str">
-        <v>GRN-2604-08</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L24" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-F3-S06</v>
       </c>
       <c r="M24" t="str">
-        <v>G4-F3-S06</v>
+        <v>MERAH</v>
       </c>
       <c r="N24" t="str">
-        <v>MERAH</v>
+        <v>RUSAK</v>
       </c>
       <c r="O24" t="str">
-        <v>RUSAK</v>
+        <v>BAGAS</v>
       </c>
       <c r="P24" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q24" t="str">
         <v/>
       </c>
     </row>
@@ -1671,27 +1607,24 @@
         <v>46134</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>GRN-2604-09</v>
       </c>
       <c r="K25" t="str">
-        <v>GRN-2604-09</v>
+        <v>MEEPLUS</v>
       </c>
       <c r="L25" t="str">
+        <v>G1-D1-S06</v>
+      </c>
+      <c r="M25" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N25" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="O25" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="M25" t="str">
-        <v>G1-D1-S06</v>
-      </c>
-      <c r="N25" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O25" t="str">
-        <v>NEW</v>
-      </c>
       <c r="P25" t="str">
-        <v>MEEPLUS</v>
-      </c>
-      <c r="Q25" t="str">
         <v/>
       </c>
     </row>
@@ -1723,28 +1656,25 @@
       <c r="I26" s="1">
         <v>46126</v>
       </c>
-      <c r="J26" s="1">
-        <v>46763</v>
+      <c r="J26" t="str">
+        <v>GRN-2604-10</v>
       </c>
       <c r="K26" t="str">
-        <v>GRN-2604-10</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L26" t="str">
-        <v>SINAR JAYA</v>
+        <v/>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>KUNING</v>
       </c>
       <c r="N26" t="str">
-        <v>KUNING</v>
+        <v>HOLD</v>
       </c>
       <c r="O26" t="str">
-        <v>HOLD</v>
+        <v>RUDI</v>
       </c>
       <c r="P26" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q26" t="str">
         <v/>
       </c>
     </row>
@@ -1776,28 +1706,25 @@
       <c r="I27" s="1">
         <v>46126</v>
       </c>
-      <c r="J27" s="1">
-        <v>46763</v>
+      <c r="J27" t="str">
+        <v>GRN-2604-10</v>
       </c>
       <c r="K27" t="str">
-        <v>GRN-2604-10</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L27" t="str">
-        <v>SINAR JAYA</v>
+        <v/>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>MERAH</v>
       </c>
       <c r="N27" t="str">
-        <v>MERAH</v>
+        <v>RUSAK</v>
       </c>
       <c r="O27" t="str">
-        <v>RUSAK</v>
+        <v>RUDI</v>
       </c>
       <c r="P27" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q27" t="str">
         <v/>
       </c>
     </row>
@@ -1830,27 +1757,24 @@
         <v>46127</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>GRN-2604-11</v>
       </c>
       <c r="K28" t="str">
-        <v>GRN-2604-11</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L28" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-F3-S12</v>
       </c>
       <c r="M28" t="str">
-        <v>G3-F3-S12</v>
+        <v>MERAH</v>
       </c>
       <c r="N28" t="str">
-        <v>MERAH</v>
+        <v>RUSAK</v>
       </c>
       <c r="O28" t="str">
-        <v>RUSAK</v>
+        <v>SITI</v>
       </c>
       <c r="P28" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q28" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -1883,27 +1807,24 @@
         <v>46127</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>GRN-2604-11</v>
       </c>
       <c r="K29" t="str">
-        <v>GRN-2604-11</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L29" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-A1-S13</v>
       </c>
       <c r="M29" t="str">
-        <v>G3-A1-S13</v>
+        <v>NEW</v>
       </c>
       <c r="N29" t="str">
-        <v>NEW</v>
+        <v>READY</v>
       </c>
       <c r="O29" t="str">
-        <v>READY</v>
+        <v>SITI</v>
       </c>
       <c r="P29" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q29" t="str">
         <v/>
       </c>
     </row>
@@ -1936,27 +1857,24 @@
         <v>46127</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>GRN-2604-11</v>
       </c>
       <c r="K30" t="str">
-        <v>GRN-2604-11</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L30" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-B4-S14</v>
       </c>
       <c r="M30" t="str">
-        <v>G3-B4-S14</v>
+        <v>HOLD</v>
       </c>
       <c r="N30" t="str">
-        <v>HOLD</v>
+        <v>READY</v>
       </c>
       <c r="O30" t="str">
-        <v>READY</v>
+        <v>SITI</v>
       </c>
       <c r="P30" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q30" t="str">
         <v/>
       </c>
     </row>
@@ -1989,27 +1907,24 @@
         <v>46128</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>GRN-2604-12</v>
       </c>
       <c r="K31" t="str">
-        <v>GRN-2604-12</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L31" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-A1-S15</v>
       </c>
       <c r="M31" t="str">
-        <v>G4-A1-S15</v>
+        <v>NEW</v>
       </c>
       <c r="N31" t="str">
-        <v>NEW</v>
+        <v>READY</v>
       </c>
       <c r="O31" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P31" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q31" t="str">
         <v/>
       </c>
     </row>
@@ -2042,27 +1957,24 @@
         <v>46128</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>GRN-2604-12</v>
       </c>
       <c r="K32" t="str">
-        <v>GRN-2604-12</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L32" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-B4-S16</v>
       </c>
       <c r="M32" t="str">
-        <v>G4-B4-S16</v>
+        <v>HOLD</v>
       </c>
       <c r="N32" t="str">
-        <v>HOLD</v>
+        <v>READY</v>
       </c>
       <c r="O32" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P32" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q32" t="str">
         <v/>
       </c>
     </row>
@@ -2095,27 +2007,24 @@
         <v>46128</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>GRN-2604-12</v>
       </c>
       <c r="K33" t="str">
-        <v>GRN-2604-12</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L33" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-C2-S17</v>
       </c>
       <c r="M33" t="str">
-        <v>G4-C2-S17</v>
+        <v>HIJAU</v>
       </c>
       <c r="N33" t="str">
-        <v>HIJAU</v>
+        <v>PENDING</v>
       </c>
       <c r="O33" t="str">
-        <v>PENDING</v>
+        <v>BAGAS</v>
       </c>
       <c r="P33" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q33" t="str">
         <v/>
       </c>
     </row>
@@ -2148,27 +2057,24 @@
         <v>46128</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>GRN-2604-12</v>
       </c>
       <c r="K34" t="str">
-        <v>GRN-2604-12</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L34" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-D1-S18</v>
       </c>
       <c r="M34" t="str">
-        <v>G4-D1-S18</v>
+        <v>HIJAU</v>
       </c>
       <c r="N34" t="str">
-        <v>HIJAU</v>
+        <v>NEW</v>
       </c>
       <c r="O34" t="str">
-        <v>NEW</v>
+        <v>BAGAS</v>
       </c>
       <c r="P34" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q34" t="str">
         <v/>
       </c>
     </row>
@@ -2200,28 +2106,25 @@
       <c r="I35" s="1">
         <v>46129</v>
       </c>
-      <c r="J35" s="1">
-        <v>46784</v>
+      <c r="J35" t="str">
+        <v>GRN-2604-13</v>
       </c>
       <c r="K35" t="str">
-        <v>GRN-2604-13</v>
+        <v>MEEPLUS</v>
       </c>
       <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v>HOLD</v>
+      </c>
+      <c r="N35" t="str">
+        <v>READY</v>
+      </c>
+      <c r="O35" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
-      <c r="N35" t="str">
-        <v>HOLD</v>
-      </c>
-      <c r="O35" t="str">
-        <v>READY</v>
-      </c>
       <c r="P35" t="str">
-        <v>MEEPLUS</v>
-      </c>
-      <c r="Q35" t="str">
         <v/>
       </c>
     </row>
@@ -2254,27 +2157,24 @@
         <v>46130</v>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>GRN-2604-14</v>
       </c>
       <c r="K36" t="str">
-        <v>GRN-2604-14</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L36" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-C2-S01</v>
       </c>
       <c r="M36" t="str">
-        <v>G2-C2-S01</v>
+        <v>HIJAU</v>
       </c>
       <c r="N36" t="str">
-        <v>HIJAU</v>
+        <v>PENDING</v>
       </c>
       <c r="O36" t="str">
-        <v>PENDING</v>
+        <v>RUDI</v>
       </c>
       <c r="P36" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q36" t="str">
         <v/>
       </c>
     </row>
@@ -2307,27 +2207,24 @@
         <v>46130</v>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>GRN-2604-14</v>
       </c>
       <c r="K37" t="str">
-        <v>GRN-2604-14</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L37" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-D1-S02</v>
       </c>
       <c r="M37" t="str">
-        <v>G2-D1-S02</v>
+        <v>HIJAU</v>
       </c>
       <c r="N37" t="str">
-        <v>HIJAU</v>
+        <v>NEW</v>
       </c>
       <c r="O37" t="str">
-        <v>NEW</v>
+        <v>RUDI</v>
       </c>
       <c r="P37" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q37" t="str">
         <v/>
       </c>
     </row>
@@ -2360,27 +2257,24 @@
         <v>46131</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>GRN-2604-15</v>
       </c>
       <c r="K38" t="str">
-        <v>GRN-2604-15</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L38" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-D1-S04</v>
       </c>
       <c r="M38" t="str">
-        <v>G3-D1-S04</v>
+        <v>HIJAU</v>
       </c>
       <c r="N38" t="str">
-        <v>HIJAU</v>
+        <v>NEW</v>
       </c>
       <c r="O38" t="str">
-        <v>NEW</v>
+        <v>SITI</v>
       </c>
       <c r="P38" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q38" t="str">
         <v/>
       </c>
     </row>
@@ -2413,27 +2307,24 @@
         <v>46131</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>GRN-2604-15</v>
       </c>
       <c r="K39" t="str">
-        <v>GRN-2604-15</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L39" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-F2-S05</v>
       </c>
       <c r="M39" t="str">
-        <v>G3-F2-S05</v>
+        <v>HIJAU</v>
       </c>
       <c r="N39" t="str">
-        <v>HIJAU</v>
+        <v>HOLD</v>
       </c>
       <c r="O39" t="str">
-        <v>HOLD</v>
+        <v>SITI</v>
       </c>
       <c r="P39" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q39" t="str">
         <v/>
       </c>
     </row>
@@ -2466,27 +2357,24 @@
         <v>46131</v>
       </c>
       <c r="J40" t="str">
-        <v/>
+        <v>GRN-2604-15</v>
       </c>
       <c r="K40" t="str">
-        <v>GRN-2604-15</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L40" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-F3-S06</v>
       </c>
       <c r="M40" t="str">
-        <v>G3-F3-S06</v>
+        <v>KUNING</v>
       </c>
       <c r="N40" t="str">
-        <v>KUNING</v>
+        <v>RUSAK</v>
       </c>
       <c r="O40" t="str">
-        <v>RUSAK</v>
+        <v>SITI</v>
       </c>
       <c r="P40" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q40" t="str">
         <v/>
       </c>
     </row>
@@ -2518,28 +2406,25 @@
       <c r="I41" s="1">
         <v>46132</v>
       </c>
-      <c r="J41" s="1">
-        <v>46805</v>
+      <c r="J41" t="str">
+        <v>GRN-2604-16</v>
       </c>
       <c r="K41" t="str">
-        <v>GRN-2604-16</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L41" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-F2-S07</v>
       </c>
       <c r="M41" t="str">
-        <v>G4-F2-S07</v>
+        <v>HIJAU</v>
       </c>
       <c r="N41" t="str">
-        <v>HIJAU</v>
+        <v>HOLD</v>
       </c>
       <c r="O41" t="str">
-        <v>HOLD</v>
+        <v>BAGAS</v>
       </c>
       <c r="P41" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q41" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -2571,28 +2456,25 @@
       <c r="I42" s="1">
         <v>46132</v>
       </c>
-      <c r="J42" s="1">
-        <v>46805</v>
+      <c r="J42" t="str">
+        <v>GRN-2604-16</v>
       </c>
       <c r="K42" t="str">
-        <v>GRN-2604-16</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L42" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-F3-S08</v>
       </c>
       <c r="M42" t="str">
-        <v>G4-F3-S08</v>
+        <v>KUNING</v>
       </c>
       <c r="N42" t="str">
-        <v>KUNING</v>
+        <v>RUSAK</v>
       </c>
       <c r="O42" t="str">
-        <v>RUSAK</v>
+        <v>BAGAS</v>
       </c>
       <c r="P42" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q42" t="str">
         <v/>
       </c>
     </row>
@@ -2624,28 +2506,25 @@
       <c r="I43" s="1">
         <v>46132</v>
       </c>
-      <c r="J43" s="1">
-        <v>46805</v>
+      <c r="J43" t="str">
+        <v>GRN-2604-16</v>
       </c>
       <c r="K43" t="str">
-        <v>GRN-2604-16</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L43" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-A1-S09</v>
       </c>
       <c r="M43" t="str">
-        <v>G4-A1-S09</v>
+        <v>MERAH</v>
       </c>
       <c r="N43" t="str">
-        <v>MERAH</v>
+        <v>READY</v>
       </c>
       <c r="O43" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P43" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q43" t="str">
         <v/>
       </c>
     </row>
@@ -2677,28 +2556,25 @@
       <c r="I44" s="1">
         <v>46132</v>
       </c>
-      <c r="J44" s="1">
-        <v>46805</v>
+      <c r="J44" t="str">
+        <v>GRN-2604-16</v>
       </c>
       <c r="K44" t="str">
-        <v>GRN-2604-16</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L44" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v>G4-B4-S10</v>
       </c>
       <c r="M44" t="str">
-        <v>G4-B4-S10</v>
+        <v>NEW</v>
       </c>
       <c r="N44" t="str">
-        <v>NEW</v>
+        <v>READY</v>
       </c>
       <c r="O44" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P44" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q44" t="str">
         <v/>
       </c>
     </row>
@@ -2731,27 +2607,24 @@
         <v>46133</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>GRN-2604-17</v>
       </c>
       <c r="K45" t="str">
-        <v>GRN-2604-17</v>
+        <v>MEEPLUS</v>
       </c>
       <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v>KUNING</v>
+      </c>
+      <c r="N45" t="str">
+        <v>RUSAK</v>
+      </c>
+      <c r="O45" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
-        <v>KUNING</v>
-      </c>
-      <c r="O45" t="str">
-        <v>RUSAK</v>
-      </c>
       <c r="P45" t="str">
-        <v>MEEPLUS</v>
-      </c>
-      <c r="Q45" t="str">
         <v/>
       </c>
     </row>
@@ -2784,27 +2657,24 @@
         <v>46134</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>GRN-2604-18</v>
       </c>
       <c r="K46" t="str">
-        <v>GRN-2604-18</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L46" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-A1-S13</v>
       </c>
       <c r="M46" t="str">
-        <v>G2-A1-S13</v>
+        <v>MERAH</v>
       </c>
       <c r="N46" t="str">
-        <v>MERAH</v>
+        <v>READY</v>
       </c>
       <c r="O46" t="str">
-        <v>READY</v>
+        <v>RUDI</v>
       </c>
       <c r="P46" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q46" t="str">
         <v/>
       </c>
     </row>
@@ -2837,27 +2707,24 @@
         <v>46134</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>GRN-2604-18</v>
       </c>
       <c r="K47" t="str">
-        <v>GRN-2604-18</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L47" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-B4-S14</v>
       </c>
       <c r="M47" t="str">
-        <v>G2-B4-S14</v>
+        <v>NEW</v>
       </c>
       <c r="N47" t="str">
-        <v>NEW</v>
+        <v>READY</v>
       </c>
       <c r="O47" t="str">
-        <v>READY</v>
+        <v>RUDI</v>
       </c>
       <c r="P47" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q47" t="str">
         <v/>
       </c>
     </row>
@@ -2889,28 +2756,25 @@
       <c r="I48" s="1">
         <v>46126</v>
       </c>
-      <c r="J48" s="1">
-        <v>46826</v>
+      <c r="J48" t="str">
+        <v>GRN-2604-19</v>
       </c>
       <c r="K48" t="str">
-        <v>GRN-2604-19</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L48" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-B4-S16</v>
       </c>
       <c r="M48" t="str">
-        <v>G3-B4-S16</v>
+        <v>NEW</v>
       </c>
       <c r="N48" t="str">
-        <v>NEW</v>
+        <v>READY</v>
       </c>
       <c r="O48" t="str">
-        <v>READY</v>
+        <v>SITI</v>
       </c>
       <c r="P48" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q48" t="str">
         <v/>
       </c>
     </row>
@@ -2942,28 +2806,25 @@
       <c r="I49" s="1">
         <v>46126</v>
       </c>
-      <c r="J49" s="1">
-        <v>46826</v>
+      <c r="J49" t="str">
+        <v>GRN-2604-19</v>
       </c>
       <c r="K49" t="str">
-        <v>GRN-2604-19</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L49" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-C2-S17</v>
       </c>
       <c r="M49" t="str">
-        <v>G3-C2-S17</v>
+        <v>HOLD</v>
       </c>
       <c r="N49" t="str">
-        <v>HOLD</v>
+        <v>PENDING</v>
       </c>
       <c r="O49" t="str">
-        <v>PENDING</v>
+        <v>SITI</v>
       </c>
       <c r="P49" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q49" t="str">
         <v/>
       </c>
     </row>
@@ -2995,28 +2856,25 @@
       <c r="I50" s="1">
         <v>46126</v>
       </c>
-      <c r="J50" s="1">
-        <v>46826</v>
+      <c r="J50" t="str">
+        <v>GRN-2604-19</v>
       </c>
       <c r="K50" t="str">
-        <v>GRN-2604-19</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L50" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-D1-S18</v>
       </c>
       <c r="M50" t="str">
-        <v>G3-D1-S18</v>
+        <v>HIJAU</v>
       </c>
       <c r="N50" t="str">
-        <v>HIJAU</v>
+        <v>NEW</v>
       </c>
       <c r="O50" t="str">
-        <v>NEW</v>
+        <v>SITI</v>
       </c>
       <c r="P50" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q50" t="str">
         <v/>
       </c>
     </row>
@@ -3049,27 +2907,24 @@
         <v>46127</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>GRN-2604-20</v>
       </c>
       <c r="K51" t="str">
-        <v>GRN-2604-20</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L51" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>HOLD</v>
       </c>
       <c r="N51" t="str">
-        <v>HOLD</v>
+        <v>PENDING</v>
       </c>
       <c r="O51" t="str">
-        <v>PENDING</v>
+        <v>BAGAS</v>
       </c>
       <c r="P51" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q51" t="str">
         <v/>
       </c>
     </row>
@@ -3102,27 +2957,24 @@
         <v>46127</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>GRN-2604-20</v>
       </c>
       <c r="K52" t="str">
-        <v>GRN-2604-20</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L52" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>HIJAU</v>
       </c>
       <c r="N52" t="str">
-        <v>HIJAU</v>
+        <v>NEW</v>
       </c>
       <c r="O52" t="str">
-        <v>NEW</v>
+        <v>BAGAS</v>
       </c>
       <c r="P52" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q52" t="str">
         <v/>
       </c>
     </row>
@@ -3155,27 +3007,24 @@
         <v>46127</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>GRN-2604-20</v>
       </c>
       <c r="K53" t="str">
-        <v>GRN-2604-20</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L53" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>HIJAU</v>
       </c>
       <c r="N53" t="str">
-        <v>HIJAU</v>
+        <v>HOLD</v>
       </c>
       <c r="O53" t="str">
-        <v>HOLD</v>
+        <v>BAGAS</v>
       </c>
       <c r="P53" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q53" t="str">
         <v/>
       </c>
     </row>
@@ -3208,27 +3057,24 @@
         <v>46127</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>GRN-2604-20</v>
       </c>
       <c r="K54" t="str">
-        <v>GRN-2604-20</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L54" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>HIJAU</v>
       </c>
       <c r="N54" t="str">
-        <v>HIJAU</v>
+        <v>RUSAK</v>
       </c>
       <c r="O54" t="str">
-        <v>RUSAK</v>
+        <v>BAGAS</v>
       </c>
       <c r="P54" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q54" t="str">
         <v/>
       </c>
     </row>
@@ -3261,27 +3107,24 @@
         <v>46128</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>GRN-2604-21</v>
       </c>
       <c r="K55" t="str">
-        <v>GRN-2604-21</v>
+        <v>MEEPLUS</v>
       </c>
       <c r="L55" t="str">
+        <v>G1-D1-S02</v>
+      </c>
+      <c r="M55" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N55" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="O55" t="str">
         <v>MEEPLUS</v>
       </c>
-      <c r="M55" t="str">
-        <v>G1-D1-S02</v>
-      </c>
-      <c r="N55" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O55" t="str">
-        <v>NEW</v>
-      </c>
       <c r="P55" t="str">
-        <v>MEEPLUS</v>
-      </c>
-      <c r="Q55" t="str">
         <v>Cek ulang isi dus</v>
       </c>
     </row>
@@ -3313,28 +3156,25 @@
       <c r="I56" s="1">
         <v>46129</v>
       </c>
-      <c r="J56" s="1">
-        <v>46847</v>
+      <c r="J56" t="str">
+        <v>GRN-2604-22</v>
       </c>
       <c r="K56" t="str">
-        <v>GRN-2604-22</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L56" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-F2-S05</v>
       </c>
       <c r="M56" t="str">
-        <v>G2-F2-S05</v>
+        <v>HIJAU</v>
       </c>
       <c r="N56" t="str">
-        <v>HIJAU</v>
+        <v>HOLD</v>
       </c>
       <c r="O56" t="str">
-        <v>HOLD</v>
+        <v>RUDI</v>
       </c>
       <c r="P56" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q56" t="str">
         <v/>
       </c>
     </row>
@@ -3366,28 +3206,25 @@
       <c r="I57" s="1">
         <v>46129</v>
       </c>
-      <c r="J57" s="1">
-        <v>46847</v>
+      <c r="J57" t="str">
+        <v>GRN-2604-22</v>
       </c>
       <c r="K57" t="str">
-        <v>GRN-2604-22</v>
+        <v>SINAR JAYA</v>
       </c>
       <c r="L57" t="str">
-        <v>SINAR JAYA</v>
+        <v>G2-F3-S06</v>
       </c>
       <c r="M57" t="str">
-        <v>G2-F3-S06</v>
+        <v>HIJAU</v>
       </c>
       <c r="N57" t="str">
-        <v>HIJAU</v>
+        <v>RUSAK</v>
       </c>
       <c r="O57" t="str">
-        <v>RUSAK</v>
+        <v>RUDI</v>
       </c>
       <c r="P57" t="str">
-        <v>RUDI</v>
-      </c>
-      <c r="Q57" t="str">
         <v/>
       </c>
     </row>
@@ -3420,27 +3257,24 @@
         <v>46130</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>GRN-2604-23</v>
       </c>
       <c r="K58" t="str">
-        <v>GRN-2604-23</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L58" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-F3-S08</v>
       </c>
       <c r="M58" t="str">
-        <v>G3-F3-S08</v>
+        <v>HIJAU</v>
       </c>
       <c r="N58" t="str">
-        <v>HIJAU</v>
+        <v>RUSAK</v>
       </c>
       <c r="O58" t="str">
-        <v>RUSAK</v>
+        <v>SITI</v>
       </c>
       <c r="P58" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q58" t="str">
         <v/>
       </c>
     </row>
@@ -3473,27 +3307,24 @@
         <v>46130</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>GRN-2604-23</v>
       </c>
       <c r="K59" t="str">
-        <v>GRN-2604-23</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L59" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-A1-S09</v>
       </c>
       <c r="M59" t="str">
-        <v>G3-A1-S09</v>
+        <v>KUNING</v>
       </c>
       <c r="N59" t="str">
-        <v>KUNING</v>
+        <v>READY</v>
       </c>
       <c r="O59" t="str">
-        <v>READY</v>
+        <v>SITI</v>
       </c>
       <c r="P59" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q59" t="str">
         <v/>
       </c>
     </row>
@@ -3526,27 +3357,24 @@
         <v>46130</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>GRN-2604-23</v>
       </c>
       <c r="K60" t="str">
-        <v>GRN-2604-23</v>
+        <v>ANUGRAH MANDIRI</v>
       </c>
       <c r="L60" t="str">
-        <v>ANUGRAH MANDIRI</v>
+        <v>G3-B4-S10</v>
       </c>
       <c r="M60" t="str">
-        <v>G3-B4-S10</v>
+        <v>MERAH</v>
       </c>
       <c r="N60" t="str">
-        <v>MERAH</v>
+        <v>READY</v>
       </c>
       <c r="O60" t="str">
-        <v>READY</v>
+        <v>SITI</v>
       </c>
       <c r="P60" t="str">
-        <v>SITI</v>
-      </c>
-      <c r="Q60" t="str">
         <v/>
       </c>
     </row>
@@ -3579,27 +3407,24 @@
         <v>46131</v>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>GRN-2604-24</v>
       </c>
       <c r="K61" t="str">
-        <v>GRN-2604-24</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L61" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>KUNING</v>
       </c>
       <c r="N61" t="str">
-        <v>KUNING</v>
+        <v>READY</v>
       </c>
       <c r="O61" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P61" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q61" t="str">
         <v/>
       </c>
     </row>
@@ -3632,27 +3457,24 @@
         <v>46131</v>
       </c>
       <c r="J62" t="str">
-        <v/>
+        <v>GRN-2604-24</v>
       </c>
       <c r="K62" t="str">
-        <v>GRN-2604-24</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L62" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>MERAH</v>
       </c>
       <c r="N62" t="str">
-        <v>MERAH</v>
+        <v>READY</v>
       </c>
       <c r="O62" t="str">
-        <v>READY</v>
+        <v>BAGAS</v>
       </c>
       <c r="P62" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q62" t="str">
         <v/>
       </c>
     </row>
@@ -3685,27 +3507,24 @@
         <v>46131</v>
       </c>
       <c r="J63" t="str">
-        <v/>
+        <v>GRN-2604-24</v>
       </c>
       <c r="K63" t="str">
-        <v>GRN-2604-24</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L63" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>NEW</v>
       </c>
       <c r="N63" t="str">
-        <v>NEW</v>
+        <v>PENDING</v>
       </c>
       <c r="O63" t="str">
-        <v>PENDING</v>
+        <v>BAGAS</v>
       </c>
       <c r="P63" t="str">
-        <v>BAGAS</v>
-      </c>
-      <c r="Q63" t="str">
         <v/>
       </c>
     </row>
@@ -3738,231 +3557,228 @@
         <v>46131</v>
       </c>
       <c r="J64" t="str">
-        <v/>
+        <v>GRN-2604-24</v>
       </c>
       <c r="K64" t="str">
-        <v>GRN-2604-24</v>
+        <v>CAHAYA LOGISTIK</v>
       </c>
       <c r="L64" t="str">
-        <v>CAHAYA LOGISTIK</v>
+        <v/>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>HOLD</v>
       </c>
       <c r="N64" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="O64" t="str">
+        <v>BAGAS</v>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="M65" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N65" t="str">
+        <v>READY</v>
+      </c>
+      <c r="O65" t="str">
+        <v>MEEPLUS</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="M66" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N66" t="str">
+        <v>READY</v>
+      </c>
+      <c r="O66" t="str">
+        <v>RUDI</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="M67" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N67" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="O67" t="str">
+        <v>SITI</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="M68" t="str">
+        <v>KUNING</v>
+      </c>
+      <c r="N68" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="O68" t="str">
+        <v>BAGAS</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="M69" t="str">
+        <v>MERAH</v>
+      </c>
+      <c r="N69" t="str">
         <v>HOLD</v>
       </c>
-      <c r="O64" t="str">
+      <c r="O69" t="str">
+        <v>MEEPLUS</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="M70" t="str">
         <v>NEW</v>
       </c>
-      <c r="P64" t="str">
+      <c r="N70" t="str">
+        <v>RUSAK</v>
+      </c>
+      <c r="O70" t="str">
+        <v>RUDI</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="M71" t="str">
+        <v>HOLD</v>
+      </c>
+      <c r="N71" t="str">
+        <v>READY</v>
+      </c>
+      <c r="O71" t="str">
+        <v>SITI</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="M72" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N72" t="str">
+        <v>READY</v>
+      </c>
+      <c r="O72" t="str">
         <v>BAGAS</v>
       </c>
-      <c r="Q64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="N65" t="str">
+    </row>
+    <row r="73">
+      <c r="M73" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="O65" t="str">
+      <c r="N73" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="O73" t="str">
+        <v>MEEPLUS</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="M74" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N74" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="O74" t="str">
+        <v>RUDI</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="M75" t="str">
+        <v>KUNING</v>
+      </c>
+      <c r="N75" t="str">
+        <v>HOLD</v>
+      </c>
+      <c r="O75" t="str">
+        <v>SITI</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="M76" t="str">
+        <v>MERAH</v>
+      </c>
+      <c r="N76" t="str">
+        <v>RUSAK</v>
+      </c>
+      <c r="O76" t="str">
+        <v>BAGAS</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="M77" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="N77" t="str">
         <v>READY</v>
       </c>
-      <c r="P65" t="str">
+      <c r="O77" t="str">
         <v>MEEPLUS</v>
       </c>
     </row>
-    <row r="66">
-      <c r="N66" t="str">
+    <row r="78">
+      <c r="M78" t="str">
+        <v>HOLD</v>
+      </c>
+      <c r="N78" t="str">
+        <v>READY</v>
+      </c>
+      <c r="O78" t="str">
+        <v>RUDI</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="M79" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="O66" t="str">
-        <v>READY</v>
-      </c>
-      <c r="P66" t="str">
-        <v>RUDI</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="N67" t="str">
+      <c r="N79" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="O79" t="str">
+        <v>SITI</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="M80" t="str">
         <v>HIJAU</v>
       </c>
-      <c r="O67" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="P67" t="str">
-        <v>SITI</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="N68" t="str">
+      <c r="N80" t="str">
+        <v>NEW</v>
+      </c>
+      <c r="O80" t="str">
+        <v>BAGAS</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="M81" t="str">
+        <v>HIJAU</v>
+      </c>
+      <c r="N81" t="str">
+        <v>HOLD</v>
+      </c>
+      <c r="O81" t="str">
+        <v>MEEPLUS</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="M82" t="str">
         <v>KUNING</v>
       </c>
-      <c r="O68" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="P68" t="str">
-        <v>BAGAS</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="N69" t="str">
-        <v>MERAH</v>
-      </c>
-      <c r="O69" t="str">
-        <v>HOLD</v>
-      </c>
-      <c r="P69" t="str">
-        <v>MEEPLUS</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="N70" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="O70" t="str">
+      <c r="N82" t="str">
         <v>RUSAK</v>
       </c>
-      <c r="P70" t="str">
-        <v>RUDI</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="N71" t="str">
-        <v>HOLD</v>
-      </c>
-      <c r="O71" t="str">
-        <v>READY</v>
-      </c>
-      <c r="P71" t="str">
-        <v>SITI</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="N72" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O72" t="str">
-        <v>READY</v>
-      </c>
-      <c r="P72" t="str">
-        <v>BAGAS</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="N73" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O73" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="P73" t="str">
-        <v>MEEPLUS</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="N74" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O74" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="P74" t="str">
-        <v>RUDI</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="N75" t="str">
-        <v>KUNING</v>
-      </c>
-      <c r="O75" t="str">
-        <v>HOLD</v>
-      </c>
-      <c r="P75" t="str">
-        <v>SITI</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="N76" t="str">
-        <v>MERAH</v>
-      </c>
-      <c r="O76" t="str">
-        <v>RUSAK</v>
-      </c>
-      <c r="P76" t="str">
-        <v>BAGAS</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="N77" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="O77" t="str">
-        <v>READY</v>
-      </c>
-      <c r="P77" t="str">
-        <v>MEEPLUS</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="N78" t="str">
-        <v>HOLD</v>
-      </c>
-      <c r="O78" t="str">
-        <v>READY</v>
-      </c>
-      <c r="P78" t="str">
-        <v>RUDI</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="N79" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O79" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="P79" t="str">
-        <v>SITI</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="N80" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O80" t="str">
-        <v>NEW</v>
-      </c>
-      <c r="P80" t="str">
-        <v>BAGAS</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="N81" t="str">
-        <v>HIJAU</v>
-      </c>
-      <c r="O81" t="str">
-        <v>HOLD</v>
-      </c>
-      <c r="P81" t="str">
-        <v>MEEPLUS</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="N82" t="str">
-        <v>KUNING</v>
-      </c>
       <c r="O82" t="str">
-        <v>RUSAK</v>
-      </c>
-      <c r="P82" t="str">
         <v>RUDI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P82"/>
   </ignoredErrors>
 </worksheet>
 </file>
